--- a/2. Dades/Anàlisi de l'assistència a les aules.xlsx
+++ b/2. Dades/Anàlisi de l'assistència a les aules.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f84440834083267/Escritorio/Universitat/TFG---Github/2. Dades/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edurne\Downloads\TFG\2. Dades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3D08A7B-C3BC-4C9D-9688-BDFEFB0F8C37}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D781F8F0-6BA3-4217-A2A9-FD526FD1A563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="15375" windowHeight="8415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15889" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16266" uniqueCount="620">
   <si>
     <t>Quin grau estudies?</t>
   </si>
@@ -1866,6 +1866,33 @@
   </si>
   <si>
     <t>38</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Política econòmica d'Espanya i de la Unió Europea. Motiu: avaluació continuada amb activitats molt participatives i d'aplicació de coneixements.</t>
+  </si>
+  <si>
+    <t>Jo assisteixo a classe independentment de si l'assignatura m'interessa o m'agrada. Considero que forma part del Pla Docent que haig de completar per a assolir el Grau.</t>
+  </si>
+  <si>
+    <t>He observat que el control d'assistència augmenta la presencialitat de l'alumnat a l'aula.</t>
+  </si>
+  <si>
+    <t>Grupos reducidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itroducció a la Investigació operativa perquè el professor explicava super bé, a poc a poc perquè puguessim seguir el ritme, era molt proper i molt entenedor </t>
+  </si>
+  <si>
+    <t>Inferència estadística perquè el professor parla com per si mateix i una miqueta enfadat i va bastant rapit, la majoria de lo que fem és teoria i no entenem gaire a les classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">que les classes siguin de matins, ara estem anant de matins però l’any que ve serà de tardes sense la possibilitat de poder escollir i molta gent no podrem assistir perquè treballem </t>
+  </si>
+  <si>
+    <t>Més pes avaluació continuada respecte l'examen final</t>
   </si>
 </sst>
 </file>
@@ -2382,8 +2409,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:EW335" totalsRowShown="0">
-  <autoFilter ref="A1:EW335" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:EW343" totalsRowShown="0">
+  <autoFilter ref="A1:EW343" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="153">
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Quin grau estudies?" dataDxfId="152"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Puntos: Quin grau estudies?" dataDxfId="151"/>
@@ -2840,13 +2867,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:EW335"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:EW343"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="153" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3307,7 +3334,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -3447,7 +3474,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="3" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -3596,7 +3623,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -3736,7 +3763,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -3876,7 +3903,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>190</v>
       </c>
@@ -4022,7 +4049,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>153</v>
       </c>
@@ -4168,7 +4195,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>199</v>
       </c>
@@ -4308,7 +4335,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -4448,7 +4475,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>199</v>
       </c>
@@ -4597,7 +4624,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="11" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>153</v>
       </c>
@@ -4746,7 +4773,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="12" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -4892,7 +4919,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="13" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>153</v>
       </c>
@@ -5032,7 +5059,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>153</v>
       </c>
@@ -5172,7 +5199,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>215</v>
       </c>
@@ -5312,7 +5339,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="16" spans="1:153" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>218</v>
       </c>
@@ -5452,7 +5479,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -5601,7 +5628,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>222</v>
       </c>
@@ -5741,7 +5768,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>222</v>
       </c>
@@ -5887,7 +5914,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="20" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>218</v>
       </c>
@@ -6033,7 +6060,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="21" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>218</v>
       </c>
@@ -6176,7 +6203,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>222</v>
       </c>
@@ -6316,7 +6343,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -6459,7 +6486,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -6608,7 +6635,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>153</v>
       </c>
@@ -6757,7 +6784,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="26" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>153</v>
       </c>
@@ -6897,7 +6924,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -7046,7 +7073,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="28" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>244</v>
       </c>
@@ -7186,7 +7213,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="29" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>190</v>
       </c>
@@ -7326,7 +7353,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="30" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>218</v>
       </c>
@@ -7472,7 +7499,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>153</v>
       </c>
@@ -7618,7 +7645,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>190</v>
       </c>
@@ -7758,7 +7785,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>153</v>
       </c>
@@ -7907,7 +7934,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -8047,7 +8074,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>153</v>
       </c>
@@ -8187,7 +8214,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>257</v>
       </c>
@@ -8327,7 +8354,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>222</v>
       </c>
@@ -8473,7 +8500,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>199</v>
       </c>
@@ -8616,7 +8643,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>153</v>
       </c>
@@ -8765,7 +8792,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="40" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>218</v>
       </c>
@@ -8905,7 +8932,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>266</v>
       </c>
@@ -9054,7 +9081,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>222</v>
       </c>
@@ -9200,7 +9227,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="43" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>218</v>
       </c>
@@ -9346,7 +9373,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="44" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>153</v>
       </c>
@@ -9486,7 +9513,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>153</v>
       </c>
@@ -9635,7 +9662,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -9775,7 +9802,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="47" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>218</v>
       </c>
@@ -9921,7 +9948,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>218</v>
       </c>
@@ -10064,7 +10091,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="49" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -10204,7 +10231,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="50" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>218</v>
       </c>
@@ -10344,7 +10371,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="51" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -10493,7 +10520,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -10642,7 +10669,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>266</v>
       </c>
@@ -10791,7 +10818,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>190</v>
       </c>
@@ -10934,7 +10961,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>153</v>
       </c>
@@ -11083,7 +11110,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="56" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>153</v>
       </c>
@@ -11223,7 +11250,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>153</v>
       </c>
@@ -11363,7 +11390,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>218</v>
       </c>
@@ -11503,7 +11530,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>153</v>
       </c>
@@ -11643,7 +11670,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>218</v>
       </c>
@@ -11789,7 +11816,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>218</v>
       </c>
@@ -11932,7 +11959,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>199</v>
       </c>
@@ -12081,7 +12108,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="63" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>215</v>
       </c>
@@ -12221,7 +12248,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>153</v>
       </c>
@@ -12361,7 +12388,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="65" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>218</v>
       </c>
@@ -12510,7 +12537,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="66" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>153</v>
       </c>
@@ -12659,7 +12686,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="67" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>266</v>
       </c>
@@ -12802,7 +12829,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>222</v>
       </c>
@@ -12951,7 +12978,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="69" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>153</v>
       </c>
@@ -13094,7 +13121,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="70" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>218</v>
       </c>
@@ -13234,7 +13261,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -13374,7 +13401,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>319</v>
       </c>
@@ -13523,7 +13550,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="73" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>218</v>
       </c>
@@ -13672,7 +13699,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="74" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>218</v>
       </c>
@@ -13815,7 +13842,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="75" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>153</v>
       </c>
@@ -13955,7 +13982,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="76" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>153</v>
       </c>
@@ -14095,7 +14122,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="77" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>319</v>
       </c>
@@ -14235,7 +14262,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>153</v>
       </c>
@@ -14378,7 +14405,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>153</v>
       </c>
@@ -14527,7 +14554,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="80" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>215</v>
       </c>
@@ -14667,7 +14694,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>215</v>
       </c>
@@ -14807,7 +14834,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="82" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>218</v>
       </c>
@@ -14947,7 +14974,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="83" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -15096,7 +15123,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="84" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>153</v>
       </c>
@@ -15236,7 +15263,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="85" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>153</v>
       </c>
@@ -15385,7 +15412,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="86" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>153</v>
       </c>
@@ -15531,7 +15558,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>153</v>
       </c>
@@ -15671,7 +15698,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="88" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>222</v>
       </c>
@@ -15811,7 +15838,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="89" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>222</v>
       </c>
@@ -15951,7 +15978,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="90" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>153</v>
       </c>
@@ -16091,7 +16118,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="91" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>222</v>
       </c>
@@ -16231,7 +16258,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="92" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>153</v>
       </c>
@@ -16371,7 +16398,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>190</v>
       </c>
@@ -16511,7 +16538,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="94" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>153</v>
       </c>
@@ -16654,7 +16681,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="95" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>153</v>
       </c>
@@ -16800,7 +16827,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="96" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>266</v>
       </c>
@@ -16946,7 +16973,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="97" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -17089,7 +17116,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="98" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>319</v>
       </c>
@@ -17229,7 +17256,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="99" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>153</v>
       </c>
@@ -17369,7 +17396,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="100" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>153</v>
       </c>
@@ -17515,7 +17542,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="101" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>153</v>
       </c>
@@ -17664,7 +17691,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="102" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>153</v>
       </c>
@@ -17804,7 +17831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>218</v>
       </c>
@@ -17947,7 +17974,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="104" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>153</v>
       </c>
@@ -18087,7 +18114,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="105" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>153</v>
       </c>
@@ -18233,7 +18260,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="106" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>153</v>
       </c>
@@ -18373,7 +18400,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="107" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>218</v>
       </c>
@@ -18522,7 +18549,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="108" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>153</v>
       </c>
@@ -18662,7 +18689,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="109" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>222</v>
       </c>
@@ -18802,7 +18829,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="110" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>199</v>
       </c>
@@ -18948,7 +18975,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="111" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>199</v>
       </c>
@@ -19091,7 +19118,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="112" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>153</v>
       </c>
@@ -19240,7 +19267,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="113" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>153</v>
       </c>
@@ -19380,7 +19407,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="114" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>153</v>
       </c>
@@ -19529,7 +19556,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="115" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>222</v>
       </c>
@@ -19669,7 +19696,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="116" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>153</v>
       </c>
@@ -19818,7 +19845,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="117" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>153</v>
       </c>
@@ -19964,7 +19991,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>218</v>
       </c>
@@ -20104,7 +20131,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="119" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>222</v>
       </c>
@@ -20244,7 +20271,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="120" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>218</v>
       </c>
@@ -20384,7 +20411,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="121" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>222</v>
       </c>
@@ -20524,7 +20551,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="122" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>199</v>
       </c>
@@ -20673,7 +20700,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="123" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>218</v>
       </c>
@@ -20813,7 +20840,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="124" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>244</v>
       </c>
@@ -20959,7 +20986,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="125" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -21105,7 +21132,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="126" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>153</v>
       </c>
@@ -21254,7 +21281,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="127" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>190</v>
       </c>
@@ -21403,7 +21430,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="128" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>153</v>
       </c>
@@ -21546,7 +21573,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="129" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>215</v>
       </c>
@@ -21686,7 +21713,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="130" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>153</v>
       </c>
@@ -21829,7 +21856,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="131" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>222</v>
       </c>
@@ -21969,7 +21996,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>199</v>
       </c>
@@ -22109,7 +22136,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="133" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>199</v>
       </c>
@@ -22249,7 +22276,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="134" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>153</v>
       </c>
@@ -22389,7 +22416,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="135" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>244</v>
       </c>
@@ -22535,7 +22562,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="136" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>153</v>
       </c>
@@ -22675,7 +22702,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="137" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>153</v>
       </c>
@@ -22824,7 +22851,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="138" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>153</v>
       </c>
@@ -22964,7 +22991,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="139" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>319</v>
       </c>
@@ -23113,7 +23140,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="140" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>222</v>
       </c>
@@ -23253,7 +23280,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="141" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>257</v>
       </c>
@@ -23393,7 +23420,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="142" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>319</v>
       </c>
@@ -23542,7 +23569,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="143" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>218</v>
       </c>
@@ -23685,7 +23712,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="144" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>257</v>
       </c>
@@ -23825,7 +23852,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="145" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>218</v>
       </c>
@@ -23965,7 +23992,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="146" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>244</v>
       </c>
@@ -24114,7 +24141,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="147" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>153</v>
       </c>
@@ -24260,7 +24287,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="148" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>153</v>
       </c>
@@ -24406,7 +24433,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="149" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>153</v>
       </c>
@@ -24552,7 +24579,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="150" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>190</v>
       </c>
@@ -24692,7 +24719,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="151" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -24832,7 +24859,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="152" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>266</v>
       </c>
@@ -24972,7 +24999,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="153" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>218</v>
       </c>
@@ -25115,7 +25142,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="154" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>266</v>
       </c>
@@ -25264,7 +25291,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="155" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>218</v>
       </c>
@@ -25407,7 +25434,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="156" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>199</v>
       </c>
@@ -25550,7 +25577,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="157" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>222</v>
       </c>
@@ -25690,7 +25717,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="158" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>153</v>
       </c>
@@ -25836,7 +25863,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="159" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>199</v>
       </c>
@@ -25976,7 +26003,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="160" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>215</v>
       </c>
@@ -26116,7 +26143,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>218</v>
       </c>
@@ -26265,7 +26292,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="162" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>266</v>
       </c>
@@ -26411,7 +26438,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="163" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>153</v>
       </c>
@@ -26560,7 +26587,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="164" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>218</v>
       </c>
@@ -26700,7 +26727,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="165" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>153</v>
       </c>
@@ -26849,7 +26876,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="166" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>153</v>
       </c>
@@ -26989,7 +27016,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="167" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>215</v>
       </c>
@@ -27138,7 +27165,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>153</v>
       </c>
@@ -27287,7 +27314,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>218</v>
       </c>
@@ -27427,7 +27454,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>222</v>
       </c>
@@ -27567,7 +27594,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="171" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>218</v>
       </c>
@@ -27707,7 +27734,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="172" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>190</v>
       </c>
@@ -27856,7 +27883,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="173" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>218</v>
       </c>
@@ -27996,7 +28023,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="174" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>153</v>
       </c>
@@ -28142,7 +28169,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="175" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>153</v>
       </c>
@@ -28291,7 +28318,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="176" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>153</v>
       </c>
@@ -28431,7 +28458,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="177" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>153</v>
       </c>
@@ -28580,7 +28607,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="178" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>153</v>
       </c>
@@ -28720,7 +28747,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="179" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>153</v>
       </c>
@@ -28860,7 +28887,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="180" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>244</v>
       </c>
@@ -29000,7 +29027,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="181" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>153</v>
       </c>
@@ -29140,7 +29167,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="182" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>153</v>
       </c>
@@ -29280,7 +29307,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="183" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>222</v>
       </c>
@@ -29420,7 +29447,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="184" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>218</v>
       </c>
@@ -29563,7 +29590,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="185" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>222</v>
       </c>
@@ -29703,7 +29730,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="186" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>244</v>
       </c>
@@ -29849,7 +29876,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="187" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>153</v>
       </c>
@@ -29989,7 +30016,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="188" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>153</v>
       </c>
@@ -30129,7 +30156,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="189" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>153</v>
       </c>
@@ -30275,7 +30302,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="190" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>199</v>
       </c>
@@ -30421,7 +30448,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="191" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>153</v>
       </c>
@@ -30561,7 +30588,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="192" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>153</v>
       </c>
@@ -30710,7 +30737,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="193" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>257</v>
       </c>
@@ -30859,7 +30886,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="194" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>218</v>
       </c>
@@ -31005,7 +31032,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="195" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>153</v>
       </c>
@@ -31145,7 +31172,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="196" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>215</v>
       </c>
@@ -31285,7 +31312,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="197" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>153</v>
       </c>
@@ -31428,7 +31455,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="198" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>153</v>
       </c>
@@ -31577,7 +31604,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="199" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>153</v>
       </c>
@@ -31726,7 +31753,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="200" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>218</v>
       </c>
@@ -31875,7 +31902,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="201" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>266</v>
       </c>
@@ -32015,7 +32042,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="202" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>190</v>
       </c>
@@ -32155,7 +32182,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="203" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>153</v>
       </c>
@@ -32295,7 +32322,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="204" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>153</v>
       </c>
@@ -32441,7 +32468,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="205" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>218</v>
       </c>
@@ -32581,7 +32608,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="206" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>218</v>
       </c>
@@ -32730,7 +32757,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="207" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>319</v>
       </c>
@@ -32873,7 +32900,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="208" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>218</v>
       </c>
@@ -33022,7 +33049,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="209" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>153</v>
       </c>
@@ -33168,7 +33195,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="210" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>218</v>
       </c>
@@ -33308,7 +33335,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="211" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>153</v>
       </c>
@@ -33457,7 +33484,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="212" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>153</v>
       </c>
@@ -33603,7 +33630,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="213" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>215</v>
       </c>
@@ -33743,7 +33770,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="214" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>215</v>
       </c>
@@ -33883,7 +33910,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="215" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>222</v>
       </c>
@@ -34026,7 +34053,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="216" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>222</v>
       </c>
@@ -34166,7 +34193,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="217" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>222</v>
       </c>
@@ -34306,7 +34333,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="218" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>222</v>
       </c>
@@ -34449,7 +34476,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="219" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -34589,7 +34616,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="220" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>215</v>
       </c>
@@ -34735,7 +34762,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="221" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>215</v>
       </c>
@@ -34875,7 +34902,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="222" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>218</v>
       </c>
@@ -35015,7 +35042,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="223" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>218</v>
       </c>
@@ -35155,7 +35182,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="224" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>218</v>
       </c>
@@ -35295,7 +35322,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="225" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>215</v>
       </c>
@@ -35444,7 +35471,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="226" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>218</v>
       </c>
@@ -35584,7 +35611,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="227" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>218</v>
       </c>
@@ -35733,7 +35760,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="228" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>222</v>
       </c>
@@ -35873,7 +35900,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="229" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>218</v>
       </c>
@@ -36016,7 +36043,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="230" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>218</v>
       </c>
@@ -36156,7 +36183,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="231" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>222</v>
       </c>
@@ -36296,7 +36323,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="232" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>222</v>
       </c>
@@ -36436,7 +36463,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="233" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>222</v>
       </c>
@@ -36585,7 +36612,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="234" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>215</v>
       </c>
@@ -36725,7 +36752,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="235" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>215</v>
       </c>
@@ -36865,7 +36892,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="236" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>215</v>
       </c>
@@ -37005,7 +37032,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="237" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>222</v>
       </c>
@@ -37145,7 +37172,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="238" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>222</v>
       </c>
@@ -37291,7 +37318,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="239" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>218</v>
       </c>
@@ -37431,7 +37458,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="240" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>222</v>
       </c>
@@ -37571,7 +37598,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="241" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>153</v>
       </c>
@@ -37720,7 +37747,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="242" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>215</v>
       </c>
@@ -37860,7 +37887,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="243" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>257</v>
       </c>
@@ -38000,7 +38027,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="244" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>257</v>
       </c>
@@ -38140,7 +38167,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="245" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>153</v>
       </c>
@@ -38280,7 +38307,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="246" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>153</v>
       </c>
@@ -38420,7 +38447,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="247" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>153</v>
       </c>
@@ -38566,7 +38593,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="248" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>153</v>
       </c>
@@ -38706,7 +38733,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="249" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>199</v>
       </c>
@@ -38846,7 +38873,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="250" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>153</v>
       </c>
@@ -38986,7 +39013,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="251" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>218</v>
       </c>
@@ -39135,7 +39162,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="252" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>218</v>
       </c>
@@ -39284,7 +39311,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="253" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>215</v>
       </c>
@@ -39424,7 +39451,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="254" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>218</v>
       </c>
@@ -39567,7 +39594,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="255" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>153</v>
       </c>
@@ -39707,7 +39734,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="256" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>218</v>
       </c>
@@ -39847,7 +39874,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="257" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>215</v>
       </c>
@@ -39996,7 +40023,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="258" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>215</v>
       </c>
@@ -40136,7 +40163,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="259" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>218</v>
       </c>
@@ -40285,7 +40312,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="260" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>218</v>
       </c>
@@ -40431,7 +40458,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="261" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>218</v>
       </c>
@@ -40571,7 +40598,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="262" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>218</v>
       </c>
@@ -40714,7 +40741,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="263" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>153</v>
       </c>
@@ -40854,7 +40881,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="264" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>218</v>
       </c>
@@ -40994,7 +41021,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="265" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>218</v>
       </c>
@@ -41134,7 +41161,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="266" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>218</v>
       </c>
@@ -41277,7 +41304,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="267" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>218</v>
       </c>
@@ -41417,7 +41444,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="268" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>218</v>
       </c>
@@ -41557,7 +41584,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="269" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>218</v>
       </c>
@@ -41706,7 +41733,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="270" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>218</v>
       </c>
@@ -41855,7 +41882,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="271" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>153</v>
       </c>
@@ -41995,7 +42022,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="272" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>218</v>
       </c>
@@ -42141,7 +42168,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="273" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>218</v>
       </c>
@@ -42281,7 +42308,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="274" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>215</v>
       </c>
@@ -42430,7 +42457,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="275" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>153</v>
       </c>
@@ -42570,7 +42597,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="276" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>218</v>
       </c>
@@ -42710,7 +42737,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="277" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>153</v>
       </c>
@@ -42850,7 +42877,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="278" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>153</v>
       </c>
@@ -42996,7 +43023,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="279" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>218</v>
       </c>
@@ -43136,7 +43163,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="280" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>218</v>
       </c>
@@ -43282,7 +43309,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="281" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>218</v>
       </c>
@@ -43422,7 +43449,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="282" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>218</v>
       </c>
@@ -43565,7 +43592,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="283" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>215</v>
       </c>
@@ -43714,7 +43741,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="284" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>218</v>
       </c>
@@ -43857,7 +43884,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="285" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>215</v>
       </c>
@@ -44003,7 +44030,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="286" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>153</v>
       </c>
@@ -44152,7 +44179,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="287" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>218</v>
       </c>
@@ -44292,7 +44319,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="288" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>218</v>
       </c>
@@ -44441,7 +44468,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="289" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>218</v>
       </c>
@@ -44584,7 +44611,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="290" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>215</v>
       </c>
@@ -44724,7 +44751,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="291" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>190</v>
       </c>
@@ -44870,7 +44897,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="292" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>215</v>
       </c>
@@ -45010,7 +45037,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="293" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>319</v>
       </c>
@@ -45150,7 +45177,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="294" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>244</v>
       </c>
@@ -45290,7 +45317,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="295" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>266</v>
       </c>
@@ -45430,7 +45457,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="296" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>244</v>
       </c>
@@ -45579,7 +45606,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="297" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>266</v>
       </c>
@@ -45728,7 +45755,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="298" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>244</v>
       </c>
@@ -45877,7 +45904,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="299" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>244</v>
       </c>
@@ -46026,7 +46053,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="300" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>222</v>
       </c>
@@ -46169,7 +46196,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="301" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>266</v>
       </c>
@@ -46309,7 +46336,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="302" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>266</v>
       </c>
@@ -46452,7 +46479,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="303" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>319</v>
       </c>
@@ -46592,7 +46619,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="304" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>244</v>
       </c>
@@ -46741,7 +46768,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="305" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>319</v>
       </c>
@@ -46884,7 +46911,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="306" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>319</v>
       </c>
@@ -47024,7 +47051,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="307" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>222</v>
       </c>
@@ -47164,7 +47191,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="308" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>319</v>
       </c>
@@ -47313,7 +47340,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="309" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>244</v>
       </c>
@@ -47456,7 +47483,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="310" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>319</v>
       </c>
@@ -47596,7 +47623,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="311" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>222</v>
       </c>
@@ -47736,7 +47763,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="312" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>244</v>
       </c>
@@ -47885,7 +47912,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="313" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>222</v>
       </c>
@@ -48031,7 +48058,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="314" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>222</v>
       </c>
@@ -48171,7 +48198,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="315" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>222</v>
       </c>
@@ -48317,7 +48344,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="316" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>244</v>
       </c>
@@ -48457,7 +48484,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="317" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>244</v>
       </c>
@@ -48606,7 +48633,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="318" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>222</v>
       </c>
@@ -48746,7 +48773,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="319" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>222</v>
       </c>
@@ -48886,7 +48913,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="320" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>244</v>
       </c>
@@ -49026,7 +49053,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="321" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>153</v>
       </c>
@@ -49175,7 +49202,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="322" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>244</v>
       </c>
@@ -49321,7 +49348,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="323" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>266</v>
       </c>
@@ -49464,7 +49491,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="324" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>218</v>
       </c>
@@ -49604,7 +49631,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="325" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>244</v>
       </c>
@@ -49744,7 +49771,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="326" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>266</v>
       </c>
@@ -49890,7 +49917,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="327" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>222</v>
       </c>
@@ -50033,7 +50060,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="328" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>218</v>
       </c>
@@ -50182,7 +50209,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="329" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>244</v>
       </c>
@@ -50331,7 +50358,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="330" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>218</v>
       </c>
@@ -50477,7 +50504,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="331" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>215</v>
       </c>
@@ -50617,7 +50644,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="332" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>153</v>
       </c>
@@ -50757,7 +50784,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="333" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>266</v>
       </c>
@@ -50897,7 +50924,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="334" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>218</v>
       </c>
@@ -51043,7 +51070,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="335" spans="1:151" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:151" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>222</v>
       </c>
@@ -51181,6 +51208,1153 @@
       </c>
       <c r="EU335" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="336" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>244</v>
+      </c>
+      <c r="D336" t="s">
+        <v>185</v>
+      </c>
+      <c r="G336" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J336" t="s">
+        <v>181</v>
+      </c>
+      <c r="M336" t="s">
+        <v>157</v>
+      </c>
+      <c r="P336" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="S336" t="s">
+        <v>173</v>
+      </c>
+      <c r="V336" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y336" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB336" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="AG336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AM336" t="s">
+        <v>164</v>
+      </c>
+      <c r="AP336" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AS336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV336" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AY336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BB336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BH336" t="s">
+        <v>167</v>
+      </c>
+      <c r="BK336" t="s">
+        <v>167</v>
+      </c>
+      <c r="BN336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BQ336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BW336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CB336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CE336" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CH336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CK336" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CN336" t="s">
+        <v>168</v>
+      </c>
+      <c r="CQ336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CT336" t="s">
+        <v>168</v>
+      </c>
+      <c r="CW336" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ336" t="s">
+        <v>168</v>
+      </c>
+      <c r="DC336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="DF336" t="s">
+        <v>168</v>
+      </c>
+      <c r="DI336" t="s">
+        <v>168</v>
+      </c>
+      <c r="DL336" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DZ336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EC336" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EF336" t="s">
+        <v>167</v>
+      </c>
+      <c r="EI336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="EL336" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="EO336" t="s">
+        <v>168</v>
+      </c>
+      <c r="ER336" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EU336" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="337" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>266</v>
+      </c>
+      <c r="D337" t="s">
+        <v>210</v>
+      </c>
+      <c r="G337" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J337" t="s">
+        <v>156</v>
+      </c>
+      <c r="M337" t="s">
+        <v>157</v>
+      </c>
+      <c r="P337" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S337" t="s">
+        <v>173</v>
+      </c>
+      <c r="V337" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y337" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB337" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="AG337" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ337" t="s">
+        <v>167</v>
+      </c>
+      <c r="AM337" t="s">
+        <v>167</v>
+      </c>
+      <c r="AP337" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV337" t="s">
+        <v>164</v>
+      </c>
+      <c r="AY337" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BB337" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE337" t="s">
+        <v>164</v>
+      </c>
+      <c r="BH337" t="s">
+        <v>164</v>
+      </c>
+      <c r="BK337" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BT337" t="s">
+        <v>167</v>
+      </c>
+      <c r="BW337" t="s">
+        <v>164</v>
+      </c>
+      <c r="CB337" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CH337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CK337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CN337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CQ337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CT337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CW337" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DC337" t="s">
+        <v>168</v>
+      </c>
+      <c r="DF337" t="s">
+        <v>168</v>
+      </c>
+      <c r="DI337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DL337" t="s">
+        <v>168</v>
+      </c>
+      <c r="DZ337" t="s">
+        <v>168</v>
+      </c>
+      <c r="EC337" t="s">
+        <v>168</v>
+      </c>
+      <c r="EF337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="EI337" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EL337" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="EO337" t="s">
+        <v>168</v>
+      </c>
+      <c r="ER337" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EU337" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="338" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>218</v>
+      </c>
+      <c r="D338" t="s">
+        <v>210</v>
+      </c>
+      <c r="G338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="J338" t="s">
+        <v>181</v>
+      </c>
+      <c r="M338" t="s">
+        <v>157</v>
+      </c>
+      <c r="P338" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="S338" t="s">
+        <v>159</v>
+      </c>
+      <c r="V338" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="Y338" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB338" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AM338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP338" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS338" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV338" t="s">
+        <v>167</v>
+      </c>
+      <c r="AY338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BB338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BE338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BH338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BK338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BN338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BQ338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BT338" t="s">
+        <v>167</v>
+      </c>
+      <c r="BW338" t="s">
+        <v>167</v>
+      </c>
+      <c r="CB338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CE338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CH338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CK338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CN338" t="s">
+        <v>167</v>
+      </c>
+      <c r="CQ338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CT338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CW338" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DC338" t="s">
+        <v>168</v>
+      </c>
+      <c r="DF338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="DI338" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DL338" t="s">
+        <v>168</v>
+      </c>
+      <c r="DO338" t="s">
+        <v>612</v>
+      </c>
+      <c r="DR338" t="s">
+        <v>613</v>
+      </c>
+      <c r="DU338" t="s">
+        <v>614</v>
+      </c>
+      <c r="DZ338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EC338" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EF338" t="s">
+        <v>167</v>
+      </c>
+      <c r="EI338" t="s">
+        <v>167</v>
+      </c>
+      <c r="EL338" t="s">
+        <v>167</v>
+      </c>
+      <c r="EO338" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="ER338" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EU338" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="339" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>153</v>
+      </c>
+      <c r="D339" t="s">
+        <v>185</v>
+      </c>
+      <c r="G339" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J339" t="s">
+        <v>216</v>
+      </c>
+      <c r="M339" t="s">
+        <v>157</v>
+      </c>
+      <c r="P339" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="S339" t="s">
+        <v>159</v>
+      </c>
+      <c r="V339" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y339" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB339" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="AG339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AP339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AY339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BB339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BE339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BH339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BK339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BN339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ339" t="s">
+        <v>167</v>
+      </c>
+      <c r="BT339" t="s">
+        <v>167</v>
+      </c>
+      <c r="BW339" t="s">
+        <v>167</v>
+      </c>
+      <c r="CB339" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE339" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CH339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CK339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CN339" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CQ339" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CT339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CW339" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DC339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="DF339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DI339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DL339" t="s">
+        <v>168</v>
+      </c>
+      <c r="DO339" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="DU339" t="s">
+        <v>615</v>
+      </c>
+      <c r="DZ339" t="s">
+        <v>168</v>
+      </c>
+      <c r="EC339" t="s">
+        <v>168</v>
+      </c>
+      <c r="EF339" t="s">
+        <v>168</v>
+      </c>
+      <c r="EI339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EL339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EO339" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="ER339" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="EU339" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="340" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>222</v>
+      </c>
+      <c r="D340" t="s">
+        <v>154</v>
+      </c>
+      <c r="G340" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J340" t="s">
+        <v>156</v>
+      </c>
+      <c r="M340" t="s">
+        <v>157</v>
+      </c>
+      <c r="P340" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S340" t="s">
+        <v>173</v>
+      </c>
+      <c r="V340" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y340" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB340" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AG340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AM340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AP340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AS340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AV340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AY340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BB340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BE340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BH340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BK340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BN340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BT340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BW340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CB340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CE340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CH340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CK340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CN340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CQ340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CT340" t="s">
+        <v>168</v>
+      </c>
+      <c r="CW340" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ340" t="s">
+        <v>168</v>
+      </c>
+      <c r="DC340" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="DF340" t="s">
+        <v>168</v>
+      </c>
+      <c r="DI340" t="s">
+        <v>168</v>
+      </c>
+      <c r="DL340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DO340" t="s">
+        <v>616</v>
+      </c>
+      <c r="DR340" t="s">
+        <v>617</v>
+      </c>
+      <c r="DU340" t="s">
+        <v>618</v>
+      </c>
+      <c r="DZ340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="EC340" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="EF340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EI340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EL340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="EO340" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="ER340" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EU340" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="341" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>218</v>
+      </c>
+      <c r="D341" t="s">
+        <v>169</v>
+      </c>
+      <c r="G341" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J341" t="s">
+        <v>156</v>
+      </c>
+      <c r="M341" t="s">
+        <v>171</v>
+      </c>
+      <c r="P341" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="S341" t="s">
+        <v>159</v>
+      </c>
+      <c r="V341" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y341" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB341" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG341" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ341" t="s">
+        <v>167</v>
+      </c>
+      <c r="AM341" t="s">
+        <v>167</v>
+      </c>
+      <c r="AP341" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS341" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AV341" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AY341" t="s">
+        <v>167</v>
+      </c>
+      <c r="BB341" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BE341" t="s">
+        <v>164</v>
+      </c>
+      <c r="BH341" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BK341" t="s">
+        <v>167</v>
+      </c>
+      <c r="BN341" t="s">
+        <v>164</v>
+      </c>
+      <c r="BQ341" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BT341" t="s">
+        <v>167</v>
+      </c>
+      <c r="BW341" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CB341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CH341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CK341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CN341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CQ341" t="s">
+        <v>167</v>
+      </c>
+      <c r="CT341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CW341" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ341" t="s">
+        <v>168</v>
+      </c>
+      <c r="DC341" t="s">
+        <v>168</v>
+      </c>
+      <c r="DF341" t="s">
+        <v>168</v>
+      </c>
+      <c r="DI341" t="s">
+        <v>168</v>
+      </c>
+      <c r="DL341" t="s">
+        <v>167</v>
+      </c>
+      <c r="DZ341" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EC341" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EF341" t="s">
+        <v>167</v>
+      </c>
+      <c r="EI341" t="s">
+        <v>167</v>
+      </c>
+      <c r="EL341" t="s">
+        <v>167</v>
+      </c>
+      <c r="EO341" t="s">
+        <v>167</v>
+      </c>
+      <c r="ER341" t="s">
+        <v>168</v>
+      </c>
+      <c r="EU341" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="342" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>218</v>
+      </c>
+      <c r="D342" t="s">
+        <v>169</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J342" t="s">
+        <v>156</v>
+      </c>
+      <c r="M342" t="s">
+        <v>157</v>
+      </c>
+      <c r="P342" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="S342" t="s">
+        <v>173</v>
+      </c>
+      <c r="V342" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y342" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB342" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG342" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ342" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM342" t="s">
+        <v>164</v>
+      </c>
+      <c r="AP342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AS342" t="s">
+        <v>164</v>
+      </c>
+      <c r="AV342" t="s">
+        <v>164</v>
+      </c>
+      <c r="AY342" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BB342" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE342" t="s">
+        <v>164</v>
+      </c>
+      <c r="BH342" t="s">
+        <v>164</v>
+      </c>
+      <c r="BK342" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN342" t="s">
+        <v>164</v>
+      </c>
+      <c r="BQ342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BT342" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BW342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CB342" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CH342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CK342" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="CN342" t="s">
+        <v>168</v>
+      </c>
+      <c r="CQ342" t="s">
+        <v>168</v>
+      </c>
+      <c r="CT342" t="s">
+        <v>168</v>
+      </c>
+      <c r="CW342" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ342" t="s">
+        <v>168</v>
+      </c>
+      <c r="DC342" t="s">
+        <v>168</v>
+      </c>
+      <c r="DF342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DI342" t="s">
+        <v>168</v>
+      </c>
+      <c r="DL342" t="s">
+        <v>168</v>
+      </c>
+      <c r="DZ342" t="s">
+        <v>168</v>
+      </c>
+      <c r="EC342" t="s">
+        <v>168</v>
+      </c>
+      <c r="EF342" t="s">
+        <v>168</v>
+      </c>
+      <c r="EI342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="EL342" t="s">
+        <v>168</v>
+      </c>
+      <c r="EO342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="ER342" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="EU342" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="343" spans="1:151" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>218</v>
+      </c>
+      <c r="D343" t="s">
+        <v>210</v>
+      </c>
+      <c r="G343" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J343" t="s">
+        <v>156</v>
+      </c>
+      <c r="M343" t="s">
+        <v>157</v>
+      </c>
+      <c r="P343" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="S343" t="s">
+        <v>159</v>
+      </c>
+      <c r="V343" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y343" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB343" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="AJ343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AM343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AP343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AS343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AV343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AY343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BB343" t="s">
+        <v>164</v>
+      </c>
+      <c r="BE343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BH343" t="s">
+        <v>164</v>
+      </c>
+      <c r="BK343" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="BQ343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="BT343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="BW343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CB343" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CH343" t="s">
+        <v>168</v>
+      </c>
+      <c r="CK343" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CN343" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="CQ343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="CT343" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="CW343" t="s">
+        <v>168</v>
+      </c>
+      <c r="CZ343" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="DC343" t="s">
+        <v>168</v>
+      </c>
+      <c r="DF343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DI343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DL343" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="DU343" t="s">
+        <v>619</v>
+      </c>
+      <c r="DZ343" t="s">
+        <v>168</v>
+      </c>
+      <c r="EC343" t="s">
+        <v>168</v>
+      </c>
+      <c r="EF343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="EI343" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="EL343" t="s">
+        <v>167</v>
+      </c>
+      <c r="EO343" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="ER343" t="s">
+        <v>168</v>
+      </c>
+      <c r="EU343" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
